--- a/datos-referencia/pos_ordenes.xlsx
+++ b/datos-referencia/pos_ordenes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="54">
   <si>
     <t>numero_po</t>
   </si>
@@ -169,10 +169,7 @@
     <t>Seguridad</t>
   </si>
   <si>
-    <t>01/07/2025</t>
-  </si>
-  <si>
-    <t>15/07/2025</t>
+    <t>2025-12-08</t>
   </si>
   <si>
     <t>ABIERTO</t>
@@ -185,16 +182,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -210,7 +199,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -218,30 +207,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,25 +511,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -582,7 +553,7 @@
         <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -605,7 +576,7 @@
         <v>51</v>
       </c>
       <c r="G3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -628,7 +599,7 @@
         <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -651,7 +622,7 @@
         <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -674,7 +645,7 @@
         <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -697,7 +668,7 @@
         <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -720,7 +691,7 @@
         <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -743,7 +714,7 @@
         <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -766,7 +737,7 @@
         <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -789,7 +760,7 @@
         <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -808,11 +779,8 @@
       <c r="E12" t="s">
         <v>46</v>
       </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -831,11 +799,8 @@
       <c r="E13" t="s">
         <v>46</v>
       </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -854,11 +819,8 @@
       <c r="E14" t="s">
         <v>46</v>
       </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -881,7 +843,7 @@
         <v>51</v>
       </c>
       <c r="G15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
